--- a/alpha_profile_oi_system/Alpha_Monthly_Paper_Trading_Journal.xlsx
+++ b/alpha_profile_oi_system/Alpha_Monthly_Paper_Trading_Journal.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y12"/>
+  <dimension ref="A1:Y13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1627,6 +1627,105 @@
         <v>100000</v>
       </c>
       <c r="Y12" t="inlineStr">
+        <is>
+          <t>SIGNAL_GENERATED_OPEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>SIG-20261027-174423-CUMMINSIND</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>27-Oct-2026</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>October 2026</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>05:44:23 PM IST</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>05:48 PM IST</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>4 Min</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>CUMMINSIND</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>BUY CALL (CE)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>CUMMINSIND26OCT4550CE</t>
+        </is>
+      </c>
+      <c r="J13" t="n">
+        <v>1</v>
+      </c>
+      <c r="K13" t="n">
+        <v>200</v>
+      </c>
+      <c r="L13" t="n">
+        <v>23</v>
+      </c>
+      <c r="M13" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="N13" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>05:59 PM IST</t>
+        </is>
+      </c>
+      <c r="P13" t="n">
+        <v>53</v>
+      </c>
+      <c r="Q13" t="inlineStr"/>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="T13" t="n">
+        <v>0</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" t="n">
+        <v>0</v>
+      </c>
+      <c r="W13" t="n">
+        <v>0</v>
+      </c>
+      <c r="X13" t="n">
+        <v>100000</v>
+      </c>
+      <c r="Y13" t="inlineStr">
         <is>
           <t>SIGNAL_GENERATED_OPEN</t>
         </is>

--- a/alpha_profile_oi_system/Alpha_Monthly_Paper_Trading_Journal.xlsx
+++ b/alpha_profile_oi_system/Alpha_Monthly_Paper_Trading_Journal.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y13"/>
+  <dimension ref="A1:Y14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1726,6 +1726,105 @@
         <v>100000</v>
       </c>
       <c r="Y13" t="inlineStr">
+        <is>
+          <t>SIGNAL_GENERATED_OPEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>SIG-20261028-095036-CHOLAFIN</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>28-Oct-2026</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>October 2026</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>09:50:36 AM IST</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>09:54 AM IST</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>4 Min</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>CHOLAFIN</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>BUY CALL (CE)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>CHOLAFIN26NOV1500CE</t>
+        </is>
+      </c>
+      <c r="J14" t="n">
+        <v>1</v>
+      </c>
+      <c r="K14" t="n">
+        <v>625</v>
+      </c>
+      <c r="L14" t="n">
+        <v>51.5</v>
+      </c>
+      <c r="M14" t="n">
+        <v>41.2</v>
+      </c>
+      <c r="N14" t="n">
+        <v>41.2</v>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>10:05 AM IST</t>
+        </is>
+      </c>
+      <c r="P14" t="n">
+        <v>92.7</v>
+      </c>
+      <c r="Q14" t="inlineStr"/>
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="T14" t="n">
+        <v>0</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" t="n">
+        <v>0</v>
+      </c>
+      <c r="W14" t="n">
+        <v>0</v>
+      </c>
+      <c r="X14" t="n">
+        <v>100000</v>
+      </c>
+      <c r="Y14" t="inlineStr">
         <is>
           <t>SIGNAL_GENERATED_OPEN</t>
         </is>

--- a/alpha_profile_oi_system/Alpha_Monthly_Paper_Trading_Journal.xlsx
+++ b/alpha_profile_oi_system/Alpha_Monthly_Paper_Trading_Journal.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y14"/>
+  <dimension ref="A1:Y16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1825,6 +1825,204 @@
         <v>100000</v>
       </c>
       <c r="Y14" t="inlineStr">
+        <is>
+          <t>SIGNAL_GENERATED_OPEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>SIG-20261028-095525-NAVINFLUOR</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>28-Oct-2026</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>October 2026</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>09:55:25 AM IST</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>09:59 AM IST</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>4 Min</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>NAVINFLUOR</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>BUY CALL (CE)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>NAVINFLUOR26NOV8500CE</t>
+        </is>
+      </c>
+      <c r="J15" t="n">
+        <v>1</v>
+      </c>
+      <c r="K15" t="n">
+        <v>500</v>
+      </c>
+      <c r="L15" t="n">
+        <v>370</v>
+      </c>
+      <c r="M15" t="n">
+        <v>296</v>
+      </c>
+      <c r="N15" t="n">
+        <v>296</v>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>10:10 AM IST</t>
+        </is>
+      </c>
+      <c r="P15" t="n">
+        <v>666</v>
+      </c>
+      <c r="Q15" t="inlineStr"/>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="T15" t="n">
+        <v>0</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" t="n">
+        <v>0</v>
+      </c>
+      <c r="W15" t="n">
+        <v>0</v>
+      </c>
+      <c r="X15" t="n">
+        <v>100000</v>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>SIGNAL_GENERATED_OPEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>SIG-20261028-095525-SIEMENS</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>28-Oct-2026</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>October 2026</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>09:55:25 AM IST</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>09:59 AM IST</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>4 Min</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>SIEMENS</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>BUY CALL (CE)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>SIEMENS26NOV3400CE</t>
+        </is>
+      </c>
+      <c r="J16" t="n">
+        <v>1</v>
+      </c>
+      <c r="K16" t="n">
+        <v>175</v>
+      </c>
+      <c r="L16" t="n">
+        <v>126.6</v>
+      </c>
+      <c r="M16" t="n">
+        <v>101.28</v>
+      </c>
+      <c r="N16" t="n">
+        <v>101.28</v>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>10:10 AM IST</t>
+        </is>
+      </c>
+      <c r="P16" t="n">
+        <v>227.88</v>
+      </c>
+      <c r="Q16" t="inlineStr"/>
+      <c r="R16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="T16" t="n">
+        <v>0</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
+      </c>
+      <c r="V16" t="n">
+        <v>0</v>
+      </c>
+      <c r="W16" t="n">
+        <v>0</v>
+      </c>
+      <c r="X16" t="n">
+        <v>100000</v>
+      </c>
+      <c r="Y16" t="inlineStr">
         <is>
           <t>SIGNAL_GENERATED_OPEN</t>
         </is>

--- a/alpha_profile_oi_system/Alpha_Monthly_Paper_Trading_Journal.xlsx
+++ b/alpha_profile_oi_system/Alpha_Monthly_Paper_Trading_Journal.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y16"/>
+  <dimension ref="A1:Y18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2023,6 +2023,204 @@
         <v>100000</v>
       </c>
       <c r="Y16" t="inlineStr">
+        <is>
+          <t>SIGNAL_GENERATED_OPEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>SIG-20261028-140042-MIDCPNIFTY</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>28-Oct-2026</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>October 2026</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>02:00:42 PM IST</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>02:04 PM IST</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>4 Min</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>MIDCPNIFTY</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>BUY PUT (PE)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>MIDCPNIFTY26NOV13300PE</t>
+        </is>
+      </c>
+      <c r="J17" t="n">
+        <v>1</v>
+      </c>
+      <c r="K17" t="n">
+        <v>120</v>
+      </c>
+      <c r="L17" t="n">
+        <v>286.15</v>
+      </c>
+      <c r="M17" t="n">
+        <v>228.92</v>
+      </c>
+      <c r="N17" t="n">
+        <v>228.92</v>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>02:15 PM IST</t>
+        </is>
+      </c>
+      <c r="P17" t="n">
+        <v>486.45</v>
+      </c>
+      <c r="Q17" t="inlineStr"/>
+      <c r="R17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="T17" t="n">
+        <v>0</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0</v>
+      </c>
+      <c r="V17" t="n">
+        <v>0</v>
+      </c>
+      <c r="W17" t="n">
+        <v>0</v>
+      </c>
+      <c r="X17" t="n">
+        <v>100000</v>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>SIGNAL_GENERATED_OPEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>SIG-20261028-140042-DATAPATTNS</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>28-Oct-2026</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>October 2026</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>02:00:42 PM IST</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>02:04 PM IST</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>4 Min</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>DATAPATTNS</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>BUY PUT (PE)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>DATAPATTNS26NOV4000PE</t>
+        </is>
+      </c>
+      <c r="J18" t="n">
+        <v>1</v>
+      </c>
+      <c r="K18" t="n">
+        <v>500</v>
+      </c>
+      <c r="L18" t="n">
+        <v>200</v>
+      </c>
+      <c r="M18" t="n">
+        <v>160</v>
+      </c>
+      <c r="N18" t="n">
+        <v>160</v>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>02:15 PM IST</t>
+        </is>
+      </c>
+      <c r="P18" t="n">
+        <v>360</v>
+      </c>
+      <c r="Q18" t="inlineStr"/>
+      <c r="R18" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="T18" t="n">
+        <v>0</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0</v>
+      </c>
+      <c r="V18" t="n">
+        <v>0</v>
+      </c>
+      <c r="W18" t="n">
+        <v>0</v>
+      </c>
+      <c r="X18" t="n">
+        <v>100000</v>
+      </c>
+      <c r="Y18" t="inlineStr">
         <is>
           <t>SIGNAL_GENERATED_OPEN</t>
         </is>

--- a/alpha_profile_oi_system/Alpha_Monthly_Paper_Trading_Journal.xlsx
+++ b/alpha_profile_oi_system/Alpha_Monthly_Paper_Trading_Journal.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y18"/>
+  <dimension ref="A1:Y19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2221,6 +2221,105 @@
         <v>100000</v>
       </c>
       <c r="Y18" t="inlineStr">
+        <is>
+          <t>SIGNAL_GENERATED_OPEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>SIG-20261028-140528-PIIND</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>28-Oct-2026</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>October 2026</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>02:05:28 PM IST</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>02:09 PM IST</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>4 Min</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>PIIND</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>BUY PUT (PE)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>PIIND26NOV2060PE</t>
+        </is>
+      </c>
+      <c r="J19" t="n">
+        <v>1</v>
+      </c>
+      <c r="K19" t="n">
+        <v>175</v>
+      </c>
+      <c r="L19" t="n">
+        <v>66.3</v>
+      </c>
+      <c r="M19" t="n">
+        <v>53.04</v>
+      </c>
+      <c r="N19" t="n">
+        <v>53.04</v>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>02:20 PM IST</t>
+        </is>
+      </c>
+      <c r="P19" t="n">
+        <v>119.34</v>
+      </c>
+      <c r="Q19" t="inlineStr"/>
+      <c r="R19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="T19" t="n">
+        <v>0</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0</v>
+      </c>
+      <c r="V19" t="n">
+        <v>0</v>
+      </c>
+      <c r="W19" t="n">
+        <v>0</v>
+      </c>
+      <c r="X19" t="n">
+        <v>100000</v>
+      </c>
+      <c r="Y19" t="inlineStr">
         <is>
           <t>SIGNAL_GENERATED_OPEN</t>
         </is>
